--- a/data/samples/DEMO02.xlsx
+++ b/data/samples/DEMO02.xlsx
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>33500</v>
+        <v>33650</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>20100</v>
+        <v>20190</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1072,7 +1072,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>10500</v>
+        <v>10350</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>18425</v>
+        <v>18508</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1435,7 +1435,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>34000</v>
+        <v>34975</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1468,7 +1468,7 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>20400</v>
+        <v>20985</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1501,7 +1501,7 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>9000</v>
+        <v>8025</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1732,7 +1732,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>18700</v>
+        <v>19236</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
